--- a/OMNI_FE_YJ2JM/OMNI_FE_BENCH.xlsx
+++ b/OMNI_FE_YJ2JM/OMNI_FE_BENCH.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yujinkang/febench/YJ2JM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jinvk/febench/OMNI_FE_YJ2JM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62476DF6-5EA9-2C44-B822-E5B5C0ECF9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44505F31-D49F-2C4A-814D-A071AEAACB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="1420" windowWidth="27640" windowHeight="16760" activeTab="3" xr2:uid="{8E7B9A9B-E4D8-BE48-B4D2-D7AD3476AD15}"/>
+    <workbookView xWindow="-28280" yWindow="4040" windowWidth="19600" windowHeight="19300" activeTab="4" xr2:uid="{8E7B9A9B-E4D8-BE48-B4D2-D7AD3476AD15}"/>
   </bookViews>
   <sheets>
     <sheet name="E_bind" sheetId="1" r:id="rId1"/>
     <sheet name="delta_E_bind" sheetId="2" r:id="rId2"/>
     <sheet name="abs(delta_E_bind)" sheetId="3" r:id="rId3"/>
     <sheet name="MAE(E_bind)" sheetId="4" r:id="rId4"/>
+    <sheet name="e_fr_energy" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="94">
   <si>
     <t>DFT</t>
   </si>
@@ -176,6 +177,150 @@
   </si>
   <si>
     <t>mlip</t>
+  </si>
+  <si>
+    <t>ompa-omat24</t>
+  </si>
+  <si>
+    <t>mace-mpa</t>
+  </si>
+  <si>
+    <t>mace-omat</t>
+  </si>
+  <si>
+    <t>orb-mpa</t>
+  </si>
+  <si>
+    <t>orb-omat</t>
+  </si>
+  <si>
+    <t>esen-omat</t>
+  </si>
+  <si>
+    <t>esen-oam</t>
+  </si>
+  <si>
+    <t>dpa-mp</t>
+  </si>
+  <si>
+    <t>dpa-omat</t>
+  </si>
+  <si>
+    <t>uma-omc</t>
+  </si>
+  <si>
+    <t>uma-omat</t>
+  </si>
+  <si>
+    <t>omni-omat24</t>
+  </si>
+  <si>
+    <t>Fe128</t>
+  </si>
+  <si>
+    <t>Fe127Vac</t>
+  </si>
+  <si>
+    <t>Fe128C</t>
+  </si>
+  <si>
+    <t>a1</t>
+  </si>
+  <si>
+    <t>a2</t>
+  </si>
+  <si>
+    <t>b1</t>
+  </si>
+  <si>
+    <t>b2</t>
+  </si>
+  <si>
+    <t>b3</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>Fe127Co</t>
+  </si>
+  <si>
+    <t>Fe126Co2</t>
+  </si>
+  <si>
+    <t>Fe127Cr</t>
+  </si>
+  <si>
+    <t>Fe126Cr2</t>
+  </si>
+  <si>
+    <t>Fe127Cu</t>
+  </si>
+  <si>
+    <t>Fe126Cu2</t>
+  </si>
+  <si>
+    <t>Fe127Mn</t>
+  </si>
+  <si>
+    <t>Fe126Mn2</t>
+  </si>
+  <si>
+    <t>Fe127Mo</t>
+  </si>
+  <si>
+    <t>Fe126Mo2</t>
+  </si>
+  <si>
+    <t>Fe127Nb</t>
+  </si>
+  <si>
+    <t>Fe126Nb2</t>
+  </si>
+  <si>
+    <t>Fe127Ni</t>
+  </si>
+  <si>
+    <t>Fe126Ni2</t>
+  </si>
+  <si>
+    <t>Fe127Ti</t>
+  </si>
+  <si>
+    <t>Fe126Ti2</t>
+  </si>
+  <si>
+    <t>Fe127V</t>
+  </si>
+  <si>
+    <t>Fe126V2</t>
   </si>
 </sst>
 </file>
@@ -239,9 +384,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -279,7 +424,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -385,7 +530,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,7 +672,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4711,4 +4856,1864 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BABAADA-9AA1-5441-ADEB-BA2156D74A32}">
+  <dimension ref="A1:P37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2">
+        <v>-1082.73657226562</v>
+      </c>
+      <c r="C2">
+        <v>-1058.55004882812</v>
+      </c>
+      <c r="D2">
+        <v>-1084.11283378385</v>
+      </c>
+      <c r="E2">
+        <v>-1062.81988749841</v>
+      </c>
+      <c r="F2">
+        <v>-1079.76953125</v>
+      </c>
+      <c r="G2">
+        <v>-1058.95458984375</v>
+      </c>
+      <c r="H2">
+        <v>-1057.85974121093</v>
+      </c>
+      <c r="I2">
+        <v>-1082.57678222656</v>
+      </c>
+      <c r="J2">
+        <v>-1075.34976077079</v>
+      </c>
+      <c r="K2">
+        <v>-1060.5933022499</v>
+      </c>
+      <c r="L2">
+        <v>-597.79496157287599</v>
+      </c>
+      <c r="M2">
+        <v>-1058.3330401472599</v>
+      </c>
+      <c r="N2">
+        <v>-1081.4375</v>
+      </c>
+      <c r="O2">
+        <v>-1058.30419921875</v>
+      </c>
+      <c r="P2">
+        <v>-1059.31201171875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3">
+        <v>-1072.03967285156</v>
+      </c>
+      <c r="C3">
+        <v>-1047.982421875</v>
+      </c>
+      <c r="D3">
+        <v>-1073.4389893063301</v>
+      </c>
+      <c r="E3">
+        <v>-1052.0398367202999</v>
+      </c>
+      <c r="F3">
+        <v>-1069.46179199218</v>
+      </c>
+      <c r="G3">
+        <v>-1048.69543457031</v>
+      </c>
+      <c r="H3">
+        <v>-1047.4453125</v>
+      </c>
+      <c r="I3">
+        <v>-1071.93505859375</v>
+      </c>
+      <c r="J3">
+        <v>-1065.1959979534099</v>
+      </c>
+      <c r="K3">
+        <v>-1050.37302315235</v>
+      </c>
+      <c r="L3">
+        <v>-593.80386829493796</v>
+      </c>
+      <c r="M3">
+        <v>-1047.9249953179999</v>
+      </c>
+      <c r="N3">
+        <v>-1070.89855957031</v>
+      </c>
+      <c r="O3">
+        <v>-1047.837890625</v>
+      </c>
+      <c r="P3">
+        <v>-1048.68469238281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4">
+        <v>-1091.17651367187</v>
+      </c>
+      <c r="C4">
+        <v>-1066.98388671875</v>
+      </c>
+      <c r="D4">
+        <v>-1092.29022962709</v>
+      </c>
+      <c r="E4">
+        <v>-1070.9231755941601</v>
+      </c>
+      <c r="F4">
+        <v>-1088.22399902343</v>
+      </c>
+      <c r="G4">
+        <v>-1067.20227050781</v>
+      </c>
+      <c r="H4">
+        <v>-1066.52734375</v>
+      </c>
+      <c r="I4">
+        <v>-1091.1845703125</v>
+      </c>
+      <c r="J4">
+        <v>-1083.7236488163401</v>
+      </c>
+      <c r="K4">
+        <v>-1068.76293903589</v>
+      </c>
+      <c r="L4">
+        <v>-602.65574605184599</v>
+      </c>
+      <c r="M4">
+        <v>-1066.78280021199</v>
+      </c>
+      <c r="N4">
+        <v>-1090.24609375</v>
+      </c>
+      <c r="O4">
+        <v>-1066.81030273437</v>
+      </c>
+      <c r="P4">
+        <v>-1067.85729980468</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5">
+        <v>-1081.18383789062</v>
+      </c>
+      <c r="C5">
+        <v>-1057.14208984375</v>
+      </c>
+      <c r="D5">
+        <v>-1082.01819646637</v>
+      </c>
+      <c r="E5">
+        <v>-1061.08979623202</v>
+      </c>
+      <c r="F5">
+        <v>-1078.51965332031</v>
+      </c>
+      <c r="G5">
+        <v>-1057.5341796875</v>
+      </c>
+      <c r="H5">
+        <v>-1056.64099121093</v>
+      </c>
+      <c r="I5">
+        <v>-1081.06652832031</v>
+      </c>
+      <c r="J5">
+        <v>-1074.16940101981</v>
+      </c>
+      <c r="K5">
+        <v>-1059.3024968802899</v>
+      </c>
+      <c r="L5">
+        <v>-595.33717194520705</v>
+      </c>
+      <c r="M5">
+        <v>-1057.0328516962099</v>
+      </c>
+      <c r="N5">
+        <v>-1080.30981445312</v>
+      </c>
+      <c r="O5">
+        <v>-1057.09155273437</v>
+      </c>
+      <c r="P5">
+        <v>-1057.9794921875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6">
+        <v>-1080.62939453125</v>
+      </c>
+      <c r="C6">
+        <v>-1056.5927734375</v>
+      </c>
+      <c r="D6">
+        <v>-1081.5754832928901</v>
+      </c>
+      <c r="E6">
+        <v>-1060.35470614513</v>
+      </c>
+      <c r="F6">
+        <v>-1077.83679199218</v>
+      </c>
+      <c r="G6">
+        <v>-1056.91284179687</v>
+      </c>
+      <c r="H6">
+        <v>-1056.064453125</v>
+      </c>
+      <c r="I6">
+        <v>-1080.52136230468</v>
+      </c>
+      <c r="J6">
+        <v>-1073.6300282739101</v>
+      </c>
+      <c r="K6">
+        <v>-1058.6461944580001</v>
+      </c>
+      <c r="L6">
+        <v>-598.70121326874096</v>
+      </c>
+      <c r="M6">
+        <v>-1056.4238581659299</v>
+      </c>
+      <c r="N6">
+        <v>-1079.71875</v>
+      </c>
+      <c r="O6">
+        <v>-1056.42944335937</v>
+      </c>
+      <c r="P6">
+        <v>-1057.32299804687</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7">
+        <v>-1071.08813476562</v>
+      </c>
+      <c r="C7">
+        <v>-1047.1923828125</v>
+      </c>
+      <c r="D7">
+        <v>-1071.78593444945</v>
+      </c>
+      <c r="E7">
+        <v>-1050.9598206446001</v>
+      </c>
+      <c r="F7">
+        <v>-1068.68884277343</v>
+      </c>
+      <c r="G7">
+        <v>-1047.84240722656</v>
+      </c>
+      <c r="H7">
+        <v>-1046.77648925781</v>
+      </c>
+      <c r="I7">
+        <v>-1070.96997070312</v>
+      </c>
+      <c r="J7">
+        <v>-1064.3745948374201</v>
+      </c>
+      <c r="K7">
+        <v>-1049.55693593621</v>
+      </c>
+      <c r="L7">
+        <v>-593.72183697656101</v>
+      </c>
+      <c r="M7">
+        <v>-1047.1513266423401</v>
+      </c>
+      <c r="N7">
+        <v>-1070.21911621093</v>
+      </c>
+      <c r="O7">
+        <v>-1047.18798828125</v>
+      </c>
+      <c r="P7">
+        <v>-1047.95092773437</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8">
+        <v>-1070.27062988281</v>
+      </c>
+      <c r="C8">
+        <v>-1046.3779296875</v>
+      </c>
+      <c r="D8">
+        <v>-1071.1913573475199</v>
+      </c>
+      <c r="E8">
+        <v>-1050.31917201741</v>
+      </c>
+      <c r="F8">
+        <v>-1067.9052734375</v>
+      </c>
+      <c r="G8">
+        <v>-1046.98999023437</v>
+      </c>
+      <c r="H8">
+        <v>-1046.19970703125</v>
+      </c>
+      <c r="I8">
+        <v>-1070.40148925781</v>
+      </c>
+      <c r="J8">
+        <v>-1063.90685790404</v>
+      </c>
+      <c r="K8">
+        <v>-1048.87652415037</v>
+      </c>
+      <c r="L8">
+        <v>-594.62572507853895</v>
+      </c>
+      <c r="M8">
+        <v>-1046.5161642888199</v>
+      </c>
+      <c r="N8">
+        <v>-1069.49145507812</v>
+      </c>
+      <c r="O8">
+        <v>-1046.31213378906</v>
+      </c>
+      <c r="P8">
+        <v>-1047.04321289062</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9">
+        <v>-1070.6953125</v>
+      </c>
+      <c r="C9">
+        <v>-1046.78442382812</v>
+      </c>
+      <c r="D9">
+        <v>-1071.4375274982599</v>
+      </c>
+      <c r="E9">
+        <v>-1050.52942310409</v>
+      </c>
+      <c r="F9">
+        <v>-1068.3759765625</v>
+      </c>
+      <c r="G9">
+        <v>-1047.44580078125</v>
+      </c>
+      <c r="H9">
+        <v>-1046.453125</v>
+      </c>
+      <c r="I9">
+        <v>-1070.66235351562</v>
+      </c>
+      <c r="J9">
+        <v>-1064.1585597097801</v>
+      </c>
+      <c r="K9">
+        <v>-1049.21551916003</v>
+      </c>
+      <c r="L9">
+        <v>-593.75508817758396</v>
+      </c>
+      <c r="M9">
+        <v>-1046.7560324528799</v>
+      </c>
+      <c r="N9">
+        <v>-1069.966796875</v>
+      </c>
+      <c r="O9">
+        <v>-1046.81420898437</v>
+      </c>
+      <c r="P9">
+        <v>-1047.5439453125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10">
+        <v>-1070.84790039062</v>
+      </c>
+      <c r="C10">
+        <v>-1046.94677734375</v>
+      </c>
+      <c r="D10">
+        <v>-1071.6030107322299</v>
+      </c>
+      <c r="E10">
+        <v>-1050.6477330343</v>
+      </c>
+      <c r="F10">
+        <v>-1068.37536621093</v>
+      </c>
+      <c r="G10">
+        <v>-1047.46594238281</v>
+      </c>
+      <c r="H10">
+        <v>-1046.46081542968</v>
+      </c>
+      <c r="I10">
+        <v>-1070.65576171875</v>
+      </c>
+      <c r="J10">
+        <v>-1064.2816712111201</v>
+      </c>
+      <c r="K10">
+        <v>-1049.40530291199</v>
+      </c>
+      <c r="L10">
+        <v>-599.06735792365998</v>
+      </c>
+      <c r="M10">
+        <v>-1046.91589878589</v>
+      </c>
+      <c r="N10">
+        <v>-1070.056640625</v>
+      </c>
+      <c r="O10">
+        <v>-1046.92626953125</v>
+      </c>
+      <c r="P10">
+        <v>-1047.71411132812</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11">
+        <v>-1070.40478515625</v>
+      </c>
+      <c r="C11">
+        <v>-1046.513671875</v>
+      </c>
+      <c r="D11">
+        <v>-1071.1201474659599</v>
+      </c>
+      <c r="E11">
+        <v>-1050.3162073022099</v>
+      </c>
+      <c r="F11">
+        <v>-1067.89489746093</v>
+      </c>
+      <c r="G11">
+        <v>-1046.99938964843</v>
+      </c>
+      <c r="H11">
+        <v>-1046.06066894531</v>
+      </c>
+      <c r="I11">
+        <v>-1070.26000976562</v>
+      </c>
+      <c r="J11">
+        <v>-1064.2816718220699</v>
+      </c>
+      <c r="K11">
+        <v>-1049.04736730083</v>
+      </c>
+      <c r="L11">
+        <v>-599.06735622071301</v>
+      </c>
+      <c r="M11">
+        <v>-1046.48218296558</v>
+      </c>
+      <c r="N11">
+        <v>-1069.6337890625</v>
+      </c>
+      <c r="O11">
+        <v>-1046.52062988281</v>
+      </c>
+      <c r="P11">
+        <v>-1047.27709960937</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12">
+        <v>-1099.70654296875</v>
+      </c>
+      <c r="C12">
+        <v>-1075.51037597656</v>
+      </c>
+      <c r="D12">
+        <v>-1100.56976921092</v>
+      </c>
+      <c r="E12">
+        <v>-1079.1290126664601</v>
+      </c>
+      <c r="F12">
+        <v>-1096.76586914062</v>
+      </c>
+      <c r="G12">
+        <v>-1075.56066894531</v>
+      </c>
+      <c r="H12">
+        <v>-1075.22668457031</v>
+      </c>
+      <c r="I12">
+        <v>-1099.83508300781</v>
+      </c>
+      <c r="J12">
+        <v>-1092.1753036379801</v>
+      </c>
+      <c r="K12">
+        <v>-1077.0367358922899</v>
+      </c>
+      <c r="L12">
+        <v>-611.47210772286201</v>
+      </c>
+      <c r="M12">
+        <v>-1075.3418742415599</v>
+      </c>
+      <c r="N12">
+        <v>-1099.09912109375</v>
+      </c>
+      <c r="O12">
+        <v>-1075.39013671875</v>
+      </c>
+      <c r="P12">
+        <v>-1076.46716308593</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13">
+        <v>-1099.70874023437</v>
+      </c>
+      <c r="C13">
+        <v>-1075.52783203125</v>
+      </c>
+      <c r="D13">
+        <v>-1100.62652265785</v>
+      </c>
+      <c r="E13">
+        <v>-1079.15303695835</v>
+      </c>
+      <c r="F13">
+        <v>-1096.72192382812</v>
+      </c>
+      <c r="G13">
+        <v>-1075.52038574218</v>
+      </c>
+      <c r="H13">
+        <v>-1075.19665527343</v>
+      </c>
+      <c r="I13">
+        <v>-1099.79077148437</v>
+      </c>
+      <c r="J13">
+        <v>-1092.1762480437701</v>
+      </c>
+      <c r="K13">
+        <v>-1077.0635018348601</v>
+      </c>
+      <c r="L13">
+        <v>-610.64860846352201</v>
+      </c>
+      <c r="M13">
+        <v>-1075.30397140953</v>
+      </c>
+      <c r="N13">
+        <v>-1099.03491210937</v>
+      </c>
+      <c r="O13">
+        <v>-1075.35791015625</v>
+      </c>
+      <c r="P13">
+        <v>-1076.44995117187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14">
+        <v>-1099.57348632812</v>
+      </c>
+      <c r="C14">
+        <v>-1075.41296386718</v>
+      </c>
+      <c r="D14">
+        <v>-1100.4831505831501</v>
+      </c>
+      <c r="E14">
+        <v>-1078.90547038866</v>
+      </c>
+      <c r="F14">
+        <v>-1096.64794921875</v>
+      </c>
+      <c r="G14">
+        <v>-1075.47412109375</v>
+      </c>
+      <c r="H14">
+        <v>-1075.05029296875</v>
+      </c>
+      <c r="I14">
+        <v>-1099.66674804687</v>
+      </c>
+      <c r="J14">
+        <v>-1092.0531853884399</v>
+      </c>
+      <c r="K14">
+        <v>-1076.96551531553</v>
+      </c>
+      <c r="L14">
+        <v>-616.34680972730905</v>
+      </c>
+      <c r="M14">
+        <v>-1075.1924754378499</v>
+      </c>
+      <c r="N14">
+        <v>-1098.90368652343</v>
+      </c>
+      <c r="O14">
+        <v>-1075.26831054687</v>
+      </c>
+      <c r="P14">
+        <v>-1076.35913085937</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15">
+        <v>-1099.76879882812</v>
+      </c>
+      <c r="C15">
+        <v>-1075.58154296875</v>
+      </c>
+      <c r="D15">
+        <v>-1100.6732084185701</v>
+      </c>
+      <c r="E15">
+        <v>-1079.11543354581</v>
+      </c>
+      <c r="F15">
+        <v>-1096.736328125</v>
+      </c>
+      <c r="G15">
+        <v>-1075.54772949218</v>
+      </c>
+      <c r="H15">
+        <v>-1075.24206542968</v>
+      </c>
+      <c r="I15">
+        <v>-1099.80432128906</v>
+      </c>
+      <c r="J15">
+        <v>-1092.1449171900699</v>
+      </c>
+      <c r="K15">
+        <v>-1077.06037735939</v>
+      </c>
+      <c r="L15">
+        <v>-614.52070320839903</v>
+      </c>
+      <c r="M15">
+        <v>-1075.3328715560201</v>
+      </c>
+      <c r="N15">
+        <v>-1099.0244140625</v>
+      </c>
+      <c r="O15">
+        <v>-1075.41088867187</v>
+      </c>
+      <c r="P15">
+        <v>-1076.47119140625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16">
+        <v>-1098.990234375</v>
+      </c>
+      <c r="C16">
+        <v>-1074.82373046875</v>
+      </c>
+      <c r="D16">
+        <v>-1099.8602292990199</v>
+      </c>
+      <c r="E16">
+        <v>-1078.37061111906</v>
+      </c>
+      <c r="F16">
+        <v>-1096.03979492187</v>
+      </c>
+      <c r="G16">
+        <v>-1074.87377929687</v>
+      </c>
+      <c r="H16">
+        <v>-1074.45520019531</v>
+      </c>
+      <c r="I16">
+        <v>-1099.07763671875</v>
+      </c>
+      <c r="J16">
+        <v>-1091.4858921095699</v>
+      </c>
+      <c r="K16">
+        <v>-1076.4002030491799</v>
+      </c>
+      <c r="L16">
+        <v>-617.938954886847</v>
+      </c>
+      <c r="M16">
+        <v>-1074.5778514144099</v>
+      </c>
+      <c r="N16">
+        <v>-1098.4140625</v>
+      </c>
+      <c r="O16">
+        <v>-1074.74780273437</v>
+      </c>
+      <c r="P16">
+        <v>-1075.86218261718</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17">
+        <v>-1097.95288085937</v>
+      </c>
+      <c r="C17">
+        <v>-1073.80236816406</v>
+      </c>
+      <c r="D17">
+        <v>-1099.09803748588</v>
+      </c>
+      <c r="E17">
+        <v>-1077.42015691598</v>
+      </c>
+      <c r="F17">
+        <v>-1095.38061523437</v>
+      </c>
+      <c r="G17">
+        <v>-1073.99047851562</v>
+      </c>
+      <c r="H17">
+        <v>-1073.56701660156</v>
+      </c>
+      <c r="I17">
+        <v>-1098.23266601562</v>
+      </c>
+      <c r="J17">
+        <v>-1090.8912852481001</v>
+      </c>
+      <c r="K17">
+        <v>-1075.6821963191001</v>
+      </c>
+      <c r="L17">
+        <v>-621.81464312812295</v>
+      </c>
+      <c r="M17">
+        <v>-1073.7691508528901</v>
+      </c>
+      <c r="N17">
+        <v>-1097.50207519531</v>
+      </c>
+      <c r="O17">
+        <v>-1073.66955566406</v>
+      </c>
+      <c r="P17">
+        <v>-1074.71044921875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18">
+        <v>-1090.19873046875</v>
+      </c>
+      <c r="C18">
+        <v>-1066.16955566406</v>
+      </c>
+      <c r="D18">
+        <v>-1090.36581312418</v>
+      </c>
+      <c r="E18">
+        <v>-1069.83734120027</v>
+      </c>
+      <c r="F18">
+        <v>-1087.37268066406</v>
+      </c>
+      <c r="G18">
+        <v>-1066.13439941406</v>
+      </c>
+      <c r="H18">
+        <v>-1065.77001953125</v>
+      </c>
+      <c r="I18">
+        <v>-1090.11669921875</v>
+      </c>
+      <c r="J18">
+        <v>-1082.9162796139699</v>
+      </c>
+      <c r="K18">
+        <v>-1068.0343015789899</v>
+      </c>
+      <c r="L18">
+        <v>-607.55791692785897</v>
+      </c>
+      <c r="M18">
+        <v>-1066.0354224298801</v>
+      </c>
+      <c r="N18">
+        <v>-1089.61303710937</v>
+      </c>
+      <c r="O18">
+        <v>-1066.23364257812</v>
+      </c>
+      <c r="P18">
+        <v>-1067.1875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19">
+        <v>-1090.28393554687</v>
+      </c>
+      <c r="C19">
+        <v>-1066.29638671875</v>
+      </c>
+      <c r="D19">
+        <v>-1090.71877786294</v>
+      </c>
+      <c r="E19">
+        <v>-1070.0168426072701</v>
+      </c>
+      <c r="F19">
+        <v>-1087.62182617187</v>
+      </c>
+      <c r="G19">
+        <v>-1066.68188476562</v>
+      </c>
+      <c r="H19">
+        <v>-1066.08349609375</v>
+      </c>
+      <c r="I19">
+        <v>-1090.46313476562</v>
+      </c>
+      <c r="J19">
+        <v>-1083.1710729077399</v>
+      </c>
+      <c r="K19">
+        <v>-1068.31489601731</v>
+      </c>
+      <c r="L19">
+        <v>-610.51373210440602</v>
+      </c>
+      <c r="M19">
+        <v>-1066.3751593683601</v>
+      </c>
+      <c r="N19">
+        <v>-1089.59936523437</v>
+      </c>
+      <c r="O19">
+        <v>-1066.38073730468</v>
+      </c>
+      <c r="P19">
+        <v>-1067.29052734375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20">
+        <v>-1081.529296875</v>
+      </c>
+      <c r="C20">
+        <v>-1057.47314453125</v>
+      </c>
+      <c r="D20">
+        <v>-1082.9081420554401</v>
+      </c>
+      <c r="E20">
+        <v>-1061.5763848379499</v>
+      </c>
+      <c r="F20">
+        <v>-1078.70458984375</v>
+      </c>
+      <c r="G20">
+        <v>-1057.86499023437</v>
+      </c>
+      <c r="H20">
+        <v>-1056.81701660156</v>
+      </c>
+      <c r="I20">
+        <v>-1081.44348144531</v>
+      </c>
+      <c r="J20">
+        <v>-1074.13918113708</v>
+      </c>
+      <c r="K20">
+        <v>-1059.36965453624</v>
+      </c>
+      <c r="L20">
+        <v>-593.09008598253502</v>
+      </c>
+      <c r="M20">
+        <v>-1057.2221988640199</v>
+      </c>
+      <c r="N20">
+        <v>-1080.2705078125</v>
+      </c>
+      <c r="O20">
+        <v>-1057.21252441406</v>
+      </c>
+      <c r="P20">
+        <v>-1058.20385742187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21">
+        <v>-1080.2711179999999</v>
+      </c>
+      <c r="C21">
+        <v>-1056.341187</v>
+      </c>
+      <c r="D21">
+        <v>-1081.6998719999999</v>
+      </c>
+      <c r="E21">
+        <v>-1060.326002</v>
+      </c>
+      <c r="F21">
+        <v>-1077.5584719999999</v>
+      </c>
+      <c r="G21">
+        <v>-1056.7308350000001</v>
+      </c>
+      <c r="H21">
+        <v>-1055.7257079999999</v>
+      </c>
+      <c r="I21">
+        <v>-1080.2452390000001</v>
+      </c>
+      <c r="J21">
+        <v>-1072.8890859999999</v>
+      </c>
+      <c r="K21">
+        <v>-1058.117033</v>
+      </c>
+      <c r="L21">
+        <v>-593.70628799999997</v>
+      </c>
+      <c r="M21">
+        <v>-1056.0753159999999</v>
+      </c>
+      <c r="N21">
+        <v>-1079.0458980000001</v>
+      </c>
+      <c r="O21">
+        <v>-1056.0649410000001</v>
+      </c>
+      <c r="P21">
+        <v>-1057.0354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22">
+        <v>-1083.96154785156</v>
+      </c>
+      <c r="C22">
+        <v>-1059.86157226562</v>
+      </c>
+      <c r="D22">
+        <v>-1085.14219609365</v>
+      </c>
+      <c r="E22">
+        <v>-1063.7667561102601</v>
+      </c>
+      <c r="F22">
+        <v>-1081.24035644531</v>
+      </c>
+      <c r="G22">
+        <v>-1060.20703125</v>
+      </c>
+      <c r="H22">
+        <v>-1059.36254882812</v>
+      </c>
+      <c r="I22">
+        <v>-1084.06799316406</v>
+      </c>
+      <c r="J22">
+        <v>-1076.38975453376</v>
+      </c>
+      <c r="K22">
+        <v>-1061.7008799314499</v>
+      </c>
+      <c r="L22">
+        <v>-594.35638234852502</v>
+      </c>
+      <c r="M22">
+        <v>-1059.7308710175901</v>
+      </c>
+      <c r="N22">
+        <v>-1082.62878417968</v>
+      </c>
+      <c r="O22">
+        <v>-1059.564453125</v>
+      </c>
+      <c r="P22">
+        <v>-1060.35791015625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23">
+        <v>-1085.045654</v>
+      </c>
+      <c r="C23">
+        <v>-1061.0261230000001</v>
+      </c>
+      <c r="D23">
+        <v>-1086.173843</v>
+      </c>
+      <c r="E23">
+        <v>-1064.711082</v>
+      </c>
+      <c r="F23">
+        <v>-1082.4532469999999</v>
+      </c>
+      <c r="G23">
+        <v>-1061.2849120000001</v>
+      </c>
+      <c r="H23">
+        <v>-1060.6069339999999</v>
+      </c>
+      <c r="I23">
+        <v>-1085.2138669999999</v>
+      </c>
+      <c r="J23">
+        <v>-1077.4662189999999</v>
+      </c>
+      <c r="K23">
+        <v>-1062.777065</v>
+      </c>
+      <c r="L23">
+        <v>-597.84788500000002</v>
+      </c>
+      <c r="M23">
+        <v>-1060.9060300000001</v>
+      </c>
+      <c r="N23">
+        <v>-1083.724976</v>
+      </c>
+      <c r="O23">
+        <v>-1060.721558</v>
+      </c>
+      <c r="P23">
+        <v>-1061.3851320000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24">
+        <v>-1077.85986328125</v>
+      </c>
+      <c r="C24">
+        <v>-1053.51965332031</v>
+      </c>
+      <c r="D24">
+        <v>-1078.95937266803</v>
+      </c>
+      <c r="E24">
+        <v>-1057.43346808757</v>
+      </c>
+      <c r="F24">
+        <v>-1074.95581054687</v>
+      </c>
+      <c r="G24">
+        <v>-1053.75952148437</v>
+      </c>
+      <c r="H24">
+        <v>-1052.78857421875</v>
+      </c>
+      <c r="I24">
+        <v>-1077.6572265625</v>
+      </c>
+      <c r="J24">
+        <v>-1070.37713301181</v>
+      </c>
+      <c r="K24">
+        <v>-1055.42518019676</v>
+      </c>
+      <c r="L24">
+        <v>-592.29709828964997</v>
+      </c>
+      <c r="M24">
+        <v>-1053.18099401211</v>
+      </c>
+      <c r="N24">
+        <v>-1076.6484375</v>
+      </c>
+      <c r="O24">
+        <v>-1053.26293945312</v>
+      </c>
+      <c r="P24">
+        <v>-1054.24621582031</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25">
+        <v>-1073.116943</v>
+      </c>
+      <c r="C25">
+        <v>-1048.6229249999999</v>
+      </c>
+      <c r="D25">
+        <v>-1073.931918</v>
+      </c>
+      <c r="E25">
+        <v>-1052.25334</v>
+      </c>
+      <c r="F25">
+        <v>-1070.2730710000001</v>
+      </c>
+      <c r="G25">
+        <v>-1048.728149</v>
+      </c>
+      <c r="H25">
+        <v>-1047.8828120000001</v>
+      </c>
+      <c r="I25">
+        <v>-1072.89563</v>
+      </c>
+      <c r="J25">
+        <v>-1065.6196990000001</v>
+      </c>
+      <c r="K25">
+        <v>-1050.4590000000001</v>
+      </c>
+      <c r="L25">
+        <v>-587.412329</v>
+      </c>
+      <c r="M25">
+        <v>-1048.2308829999999</v>
+      </c>
+      <c r="N25">
+        <v>-1071.97876</v>
+      </c>
+      <c r="O25">
+        <v>-1048.365845</v>
+      </c>
+      <c r="P25">
+        <v>-1049.325073</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26">
+        <v>-1083.14147949218</v>
+      </c>
+      <c r="C26">
+        <v>-1058.98400878906</v>
+      </c>
+      <c r="D26">
+        <v>-1084.39766488397</v>
+      </c>
+      <c r="E26">
+        <v>-1063.3899257539999</v>
+      </c>
+      <c r="F26">
+        <v>-1080.42858886718</v>
+      </c>
+      <c r="G26">
+        <v>-1059.47802734375</v>
+      </c>
+      <c r="H26">
+        <v>-1058.48840332031</v>
+      </c>
+      <c r="I26">
+        <v>-1083.17687988281</v>
+      </c>
+      <c r="J26">
+        <v>-1075.87714505195</v>
+      </c>
+      <c r="K26">
+        <v>-1061.07950472831</v>
+      </c>
+      <c r="L26">
+        <v>-593.19641131037702</v>
+      </c>
+      <c r="M26">
+        <v>-1058.8378714984799</v>
+      </c>
+      <c r="N26">
+        <v>-1081.859375</v>
+      </c>
+      <c r="O26">
+        <v>-1058.75634765625</v>
+      </c>
+      <c r="P26">
+        <v>-1059.61303710937</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27">
+        <v>-1083.6232910000001</v>
+      </c>
+      <c r="C27">
+        <v>-1059.4952390000001</v>
+      </c>
+      <c r="D27">
+        <v>-1084.7353310000001</v>
+      </c>
+      <c r="E27">
+        <v>-1063.9607309999999</v>
+      </c>
+      <c r="F27">
+        <v>-1081.055664</v>
+      </c>
+      <c r="G27">
+        <v>-1060.0076899999999</v>
+      </c>
+      <c r="H27">
+        <v>-1059.1195070000001</v>
+      </c>
+      <c r="I27">
+        <v>-1083.765625</v>
+      </c>
+      <c r="J27">
+        <v>-1076.451231</v>
+      </c>
+      <c r="K27">
+        <v>-1061.625444</v>
+      </c>
+      <c r="L27">
+        <v>-595.64455299999997</v>
+      </c>
+      <c r="M27">
+        <v>-1059.3689629999999</v>
+      </c>
+      <c r="N27">
+        <v>-1082.345337</v>
+      </c>
+      <c r="O27">
+        <v>-1059.274048</v>
+      </c>
+      <c r="P27">
+        <v>-1059.9938959999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28">
+        <v>-1084.92651367187</v>
+      </c>
+      <c r="C28">
+        <v>-1061.00805664062</v>
+      </c>
+      <c r="D28">
+        <v>-1086.2908521203101</v>
+      </c>
+      <c r="E28">
+        <v>-1065.0582707588601</v>
+      </c>
+      <c r="F28">
+        <v>-1082.26635742187</v>
+      </c>
+      <c r="G28">
+        <v>-1061.43920898437</v>
+      </c>
+      <c r="H28">
+        <v>-1060.62182617187</v>
+      </c>
+      <c r="I28">
+        <v>-1085.08056640625</v>
+      </c>
+      <c r="J28">
+        <v>-1077.6464014053299</v>
+      </c>
+      <c r="K28">
+        <v>-1063.00690412521</v>
+      </c>
+      <c r="L28">
+        <v>-595.30272583975898</v>
+      </c>
+      <c r="M28">
+        <v>-1060.93162920792</v>
+      </c>
+      <c r="N28">
+        <v>-1083.64855957031</v>
+      </c>
+      <c r="O28">
+        <v>-1060.77563476562</v>
+      </c>
+      <c r="P28">
+        <v>-1061.55322265625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29">
+        <v>-1086.931519</v>
+      </c>
+      <c r="C29">
+        <v>-1063.2751459999999</v>
+      </c>
+      <c r="D29">
+        <v>-1088.3344400000001</v>
+      </c>
+      <c r="E29">
+        <v>-1067.184976</v>
+      </c>
+      <c r="F29">
+        <v>-1084.4959719999999</v>
+      </c>
+      <c r="G29">
+        <v>-1063.7875979999999</v>
+      </c>
+      <c r="H29">
+        <v>-1063.126953</v>
+      </c>
+      <c r="I29">
+        <v>-1087.2801509999999</v>
+      </c>
+      <c r="J29">
+        <v>-1079.7580829999999</v>
+      </c>
+      <c r="K29">
+        <v>-1065.2321440000001</v>
+      </c>
+      <c r="L29">
+        <v>-591.26522699999998</v>
+      </c>
+      <c r="M29">
+        <v>-1063.2898769999999</v>
+      </c>
+      <c r="N29">
+        <v>-1085.7448730000001</v>
+      </c>
+      <c r="O29">
+        <v>-1063.134644</v>
+      </c>
+      <c r="P29">
+        <v>-1063.750732</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30">
+        <v>-1084.37158203125</v>
+      </c>
+      <c r="C30">
+        <v>-1060.30639648437</v>
+      </c>
+      <c r="D30">
+        <v>-1085.7528951403499</v>
+      </c>
+      <c r="E30">
+        <v>-1064.1309993570501</v>
+      </c>
+      <c r="F30">
+        <v>-1081.66809082031</v>
+      </c>
+      <c r="G30">
+        <v>-1060.86206054687</v>
+      </c>
+      <c r="H30">
+        <v>-1059.85424804687</v>
+      </c>
+      <c r="I30">
+        <v>-1084.44738769531</v>
+      </c>
+      <c r="J30">
+        <v>-1077.06793832778</v>
+      </c>
+      <c r="K30">
+        <v>-1062.27357131242</v>
+      </c>
+      <c r="L30">
+        <v>-600.27732631235301</v>
+      </c>
+      <c r="M30">
+        <v>-1060.2321617263799</v>
+      </c>
+      <c r="N30">
+        <v>-1083.21069335937</v>
+      </c>
+      <c r="O30">
+        <v>-1060.19213867187</v>
+      </c>
+      <c r="P30">
+        <v>-1060.98522949218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31">
+        <v>-1085.6489260000001</v>
+      </c>
+      <c r="C31">
+        <v>-1061.706543</v>
+      </c>
+      <c r="D31">
+        <v>-1087.0739189999999</v>
+      </c>
+      <c r="E31">
+        <v>-1065.241037</v>
+      </c>
+      <c r="F31">
+        <v>-1083.1982419999999</v>
+      </c>
+      <c r="G31">
+        <v>-1062.4426269999999</v>
+      </c>
+      <c r="H31">
+        <v>-1061.5177000000001</v>
+      </c>
+      <c r="I31">
+        <v>-1085.9219969999999</v>
+      </c>
+      <c r="J31">
+        <v>-1078.4820259999999</v>
+      </c>
+      <c r="K31">
+        <v>-1063.6455940000001</v>
+      </c>
+      <c r="L31">
+        <v>-597.83577500000001</v>
+      </c>
+      <c r="M31">
+        <v>-1061.801281</v>
+      </c>
+      <c r="N31">
+        <v>-1084.674927</v>
+      </c>
+      <c r="O31">
+        <v>-1061.7619629999999</v>
+      </c>
+      <c r="P31">
+        <v>-1062.376221</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32">
+        <v>-1079.98815917968</v>
+      </c>
+      <c r="C32">
+        <v>-1055.71044921875</v>
+      </c>
+      <c r="D32">
+        <v>-1081.25996017797</v>
+      </c>
+      <c r="E32">
+        <v>-1059.7743369391101</v>
+      </c>
+      <c r="F32">
+        <v>-1077.13977050781</v>
+      </c>
+      <c r="G32">
+        <v>-1056.0673828125</v>
+      </c>
+      <c r="H32">
+        <v>-1055.07983398437</v>
+      </c>
+      <c r="I32">
+        <v>-1079.93176269531</v>
+      </c>
+      <c r="J32">
+        <v>-1072.5673969984</v>
+      </c>
+      <c r="K32">
+        <v>-1057.6667238473799</v>
+      </c>
+      <c r="L32">
+        <v>-593.71790939417497</v>
+      </c>
+      <c r="M32">
+        <v>-1055.45638339739</v>
+      </c>
+      <c r="N32">
+        <v>-1078.78784179687</v>
+      </c>
+      <c r="O32">
+        <v>-1055.5234375</v>
+      </c>
+      <c r="P32">
+        <v>-1056.44555664062</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33">
+        <v>-1077.2717290000001</v>
+      </c>
+      <c r="C33">
+        <v>-1052.9033199999999</v>
+      </c>
+      <c r="D33">
+        <v>-1078.4835009999999</v>
+      </c>
+      <c r="E33">
+        <v>-1056.8501249999999</v>
+      </c>
+      <c r="F33">
+        <v>-1074.5473629999999</v>
+      </c>
+      <c r="G33">
+        <v>-1053.245361</v>
+      </c>
+      <c r="H33">
+        <v>-1052.310913</v>
+      </c>
+      <c r="I33">
+        <v>-1077.2641599999999</v>
+      </c>
+      <c r="J33">
+        <v>-1069.8057449999999</v>
+      </c>
+      <c r="K33">
+        <v>-1054.7902240000001</v>
+      </c>
+      <c r="L33">
+        <v>-596.70570099999998</v>
+      </c>
+      <c r="M33">
+        <v>-1052.608978</v>
+      </c>
+      <c r="N33">
+        <v>-1076.1594239999999</v>
+      </c>
+      <c r="O33">
+        <v>-1052.771362</v>
+      </c>
+      <c r="P33">
+        <v>-1053.614746</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34">
+        <v>-1082.94360351562</v>
+      </c>
+      <c r="C34">
+        <v>-1058.82568359375</v>
+      </c>
+      <c r="D34">
+        <v>-1084.3304084505601</v>
+      </c>
+      <c r="E34">
+        <v>-1062.61993087938</v>
+      </c>
+      <c r="F34">
+        <v>-1080.18481445312</v>
+      </c>
+      <c r="G34">
+        <v>-1059.27990722656</v>
+      </c>
+      <c r="H34">
+        <v>-1058.21997070312</v>
+      </c>
+      <c r="I34">
+        <v>-1082.8447265625</v>
+      </c>
+      <c r="J34">
+        <v>-1075.7035559415799</v>
+      </c>
+      <c r="K34">
+        <v>-1060.79206354543</v>
+      </c>
+      <c r="L34">
+        <v>-595.12000662486105</v>
+      </c>
+      <c r="M34">
+        <v>-1058.6627920932101</v>
+      </c>
+      <c r="N34">
+        <v>-1081.76489257812</v>
+      </c>
+      <c r="O34">
+        <v>-1058.70385742187</v>
+      </c>
+      <c r="P34">
+        <v>-1059.58251953125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35">
+        <v>-1082.817505</v>
+      </c>
+      <c r="C35">
+        <v>-1058.767212</v>
+      </c>
+      <c r="D35">
+        <v>-1084.077796</v>
+      </c>
+      <c r="E35">
+        <v>-1062.170539</v>
+      </c>
+      <c r="F35">
+        <v>-1080.249634</v>
+      </c>
+      <c r="G35">
+        <v>-1059.29126</v>
+      </c>
+      <c r="H35">
+        <v>-1058.3061520000001</v>
+      </c>
+      <c r="I35">
+        <v>-1082.8131100000001</v>
+      </c>
+      <c r="J35">
+        <v>-1075.7593380000001</v>
+      </c>
+      <c r="K35">
+        <v>-1060.720229</v>
+      </c>
+      <c r="L35">
+        <v>-589.36352099999999</v>
+      </c>
+      <c r="M35">
+        <v>-1058.7445279999999</v>
+      </c>
+      <c r="N35">
+        <v>-1081.8623050000001</v>
+      </c>
+      <c r="O35">
+        <v>-1058.8486330000001</v>
+      </c>
+      <c r="P35">
+        <v>-1059.5979</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36">
+        <v>-1083.98657226562</v>
+      </c>
+      <c r="C36">
+        <v>-1059.83471679687</v>
+      </c>
+      <c r="D36">
+        <v>-1085.3308624030401</v>
+      </c>
+      <c r="E36">
+        <v>-1063.74179492548</v>
+      </c>
+      <c r="F36">
+        <v>-1081.29724121093</v>
+      </c>
+      <c r="G36">
+        <v>-1060.28979492187</v>
+      </c>
+      <c r="H36">
+        <v>-1059.32250976562</v>
+      </c>
+      <c r="I36">
+        <v>-1084.04089355468</v>
+      </c>
+      <c r="J36">
+        <v>-1076.6763496398901</v>
+      </c>
+      <c r="K36">
+        <v>-1061.7738573551101</v>
+      </c>
+      <c r="L36">
+        <v>-595.60400076567703</v>
+      </c>
+      <c r="M36">
+        <v>-1059.7203324529601</v>
+      </c>
+      <c r="N36">
+        <v>-1082.77783203125</v>
+      </c>
+      <c r="O36">
+        <v>-1059.68530273437</v>
+      </c>
+      <c r="P36">
+        <v>-1060.46020507812</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37">
+        <v>-1084.9575199999999</v>
+      </c>
+      <c r="C37">
+        <v>-1060.8266599999999</v>
+      </c>
+      <c r="D37">
+        <v>-1086.405988</v>
+      </c>
+      <c r="E37">
+        <v>-1064.537642</v>
+      </c>
+      <c r="F37">
+        <v>-1082.5139160000001</v>
+      </c>
+      <c r="G37">
+        <v>-1061.3520510000001</v>
+      </c>
+      <c r="H37">
+        <v>-1060.5301509999999</v>
+      </c>
+      <c r="I37">
+        <v>-1085.211548</v>
+      </c>
+      <c r="J37">
+        <v>-1077.8063299999999</v>
+      </c>
+      <c r="K37">
+        <v>-1062.7845689999999</v>
+      </c>
+      <c r="L37">
+        <v>-590.14359300000001</v>
+      </c>
+      <c r="M37">
+        <v>-1060.8904460000001</v>
+      </c>
+      <c r="N37">
+        <v>-1083.9111330000001</v>
+      </c>
+      <c r="O37">
+        <v>-1060.8295900000001</v>
+      </c>
+      <c r="P37">
+        <v>-1061.4073490000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>